--- a/changes/556-ammo-super.xlsx
+++ b/changes/556-ammo-super.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683AC1CA-D616-48A1-99DB-B19E82CC249B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AC4AD4-B4CA-4543-941F-8C95A5A99EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -808,11 +808,17 @@
     <xf numFmtId="164" fontId="7" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -820,12 +826,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -913,7 +913,9 @@
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="weighted_damage"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="velocity_drop"/>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="suppression"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="bullet_penetration_ability"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="bullet_penetration_ability">
+      <calculatedColumnFormula>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="pen_low"/>
     <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="pen_high"/>
     <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="pen_velocity_low"/>
@@ -1139,70 +1141,70 @@
     <col min="3" max="8" width="5.625" customWidth="1"/>
     <col min="9" max="9" width="8" customWidth="1"/>
     <col min="10" max="28" width="5.625" customWidth="1"/>
-    <col min="29" max="29" width="24.875" customWidth="1"/>
+    <col min="29" max="29" width="31" customWidth="1"/>
     <col min="30" max="36" width="5.625" customWidth="1"/>
     <col min="37" max="37" width="9.625" customWidth="1"/>
     <col min="38" max="43" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="24" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="47" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="46"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="45"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="48" t="s">
+      <c r="S1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="47" t="s">
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="45"/>
-      <c r="AD1" s="45"/>
-      <c r="AE1" s="45"/>
-      <c r="AF1" s="45"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="49" t="s">
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="45"/>
+      <c r="AH1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="46"/>
-      <c r="AJ1" s="50" t="s">
+      <c r="AI1" s="45"/>
+      <c r="AJ1" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="46"/>
-      <c r="AL1" s="51" t="s">
+      <c r="AK1" s="45"/>
+      <c r="AL1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AM1" s="45"/>
-      <c r="AN1" s="45"/>
-      <c r="AO1" s="45"/>
-      <c r="AP1" s="45"/>
-      <c r="AQ1" s="46"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="47"/>
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="45"/>
     </row>
     <row r="2" spans="1:43" ht="45.75" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -1425,14 +1427,14 @@
         <v>0.75</v>
       </c>
       <c r="AC3" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD3,";",'556-ammo'!$AE3,";",'556-ammo'!$AF3,";",'556-ammo'!$AG3,")")</f>
-        <v>stat(bullet_velocity;0.35;1.15;1500;3000)</v>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
+        <v>stat(bullet_velocity;0.3;0.8;1500;3000)</v>
       </c>
       <c r="AD3" s="13">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="AE3" s="13">
-        <v>1.1499999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AF3" s="14">
         <v>1500</v>
@@ -1446,7 +1448,7 @@
       </c>
       <c r="AI3" s="11">
         <f t="shared" ref="AI3:AI13" si="0">MAX(AD3,MIN(AE3,AD3+(AH3-AF3)*(AE3-AD3)/(AG3-AF3)))</f>
-        <v>0.79959999999999998</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="AJ3" s="16">
         <v>36</v>
@@ -1472,11 +1474,11 @@
       </c>
       <c r="AP3" s="18">
         <f>(AI3-Model!$B$8)*Model!$B$38</f>
-        <v>-0.80160000000000009</v>
+        <v>-1.6760000000000002</v>
       </c>
       <c r="AQ3" s="18">
         <f t="shared" ref="AQ3:AQ13" si="1">SUM(AL3:AP3)</f>
-        <v>-2.1265999999999958</v>
+        <v>-3.0009999999999959</v>
       </c>
     </row>
     <row r="4" spans="1:43" ht="14.25" customHeight="1">
@@ -1569,14 +1571,14 @@
         <v>0.8</v>
       </c>
       <c r="AC4" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD4,";",'556-ammo'!$AE4,";",'556-ammo'!$AF4,";",'556-ammo'!$AG4,")")</f>
-        <v>stat(bullet_velocity;0.45;1.25;1500;3000)</v>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
+        <v>stat(bullet_velocity;0.4;0.9;1500;3000)</v>
       </c>
       <c r="AD4" s="13">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="AE4" s="13">
-        <v>1.25</v>
+        <v>0.9</v>
       </c>
       <c r="AF4" s="14">
         <v>1500</v>
@@ -1590,7 +1592,7 @@
       </c>
       <c r="AI4" s="11">
         <f t="shared" si="0"/>
-        <v>0.84626666666666672</v>
+        <v>0.64766666666666672</v>
       </c>
       <c r="AJ4" s="19">
         <v>38</v>
@@ -1616,11 +1618,11 @@
       </c>
       <c r="AP4" s="21">
         <f>(AI4-Model!$B$8)*Model!$B$38</f>
-        <v>-0.61493333333333311</v>
+        <v>-1.4093333333333331</v>
       </c>
       <c r="AQ4" s="21">
         <f t="shared" si="1"/>
-        <v>-1.8149333333333311</v>
+        <v>-2.6093333333333311</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="14.25" customHeight="1">
@@ -1713,7 +1715,7 @@
         <v>0.5</v>
       </c>
       <c r="AC5" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD5,";",'556-ammo'!$AE5,";",'556-ammo'!$AF5,";",'556-ammo'!$AG5,")")</f>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0;0.15;1500;3000)</v>
       </c>
       <c r="AD5" s="13">
@@ -1857,14 +1859,14 @@
         <v>1.05</v>
       </c>
       <c r="AC6" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD6,";",'556-ammo'!$AE6,";",'556-ammo'!$AF6,";",'556-ammo'!$AG6,")")</f>
-        <v>stat(bullet_velocity;0.45;1.25;1500;3000)</v>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
+        <v>stat(bullet_velocity;0.35;0.85;1500;3000)</v>
       </c>
       <c r="AD6" s="13">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="AE6" s="13">
-        <v>1.25</v>
+        <v>0.85</v>
       </c>
       <c r="AF6" s="14">
         <v>1500</v>
@@ -1878,7 +1880,7 @@
       </c>
       <c r="AI6" s="24">
         <f t="shared" si="0"/>
-        <v>0.85960000000000014</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="AJ6" s="19">
         <v>37</v>
@@ -1904,11 +1906,11 @@
       </c>
       <c r="AP6" s="21">
         <f>(AI6-Model!$B$8)*Model!$B$38</f>
-        <v>-0.56159999999999943</v>
+        <v>-1.5760000000000001</v>
       </c>
       <c r="AQ6" s="21">
         <f t="shared" si="1"/>
-        <v>0.41340000000000698</v>
+        <v>-0.60099999999999365</v>
       </c>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1">
@@ -2001,14 +2003,14 @@
         <v>0.85</v>
       </c>
       <c r="AC7" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD7,";",'556-ammo'!$AE7,";",'556-ammo'!$AF7,";",'556-ammo'!$AG7,")")</f>
-        <v>stat(bullet_velocity;0.45;1.25;1500;3000)</v>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
+        <v>stat(bullet_velocity;0.35;0.85;1500;3000)</v>
       </c>
       <c r="AD7" s="13">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="AE7" s="13">
-        <v>1.25</v>
+        <v>0.85</v>
       </c>
       <c r="AF7" s="14">
         <v>1500</v>
@@ -2022,7 +2024,7 @@
       </c>
       <c r="AI7" s="11">
         <f t="shared" si="0"/>
-        <v>0.92626666666666679</v>
+        <v>0.64766666666666661</v>
       </c>
       <c r="AJ7" s="16">
         <v>32</v>
@@ -2048,11 +2050,11 @@
       </c>
       <c r="AP7" s="18">
         <f>(AI7-Model!$B$8)*Model!$B$38</f>
-        <v>-0.29493333333333283</v>
+        <v>-1.4093333333333335</v>
       </c>
       <c r="AQ7" s="18">
         <f t="shared" si="1"/>
-        <v>0.21506666666667629</v>
+        <v>-0.89933333333332444</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1">
@@ -2145,7 +2147,7 @@
         <v>0.85</v>
       </c>
       <c r="AC8" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD8,";",'556-ammo'!$AE8,";",'556-ammo'!$AF8,";",'556-ammo'!$AG8,")")</f>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0;0.35;1500;3000)</v>
       </c>
       <c r="AD8" s="13">
@@ -2289,14 +2291,14 @@
         <v>0.8</v>
       </c>
       <c r="AC9" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD9,";",'556-ammo'!$AE9,";",'556-ammo'!$AF9,";",'556-ammo'!$AG9,")")</f>
-        <v>stat(bullet_velocity;0.2;1;1500;3000)</v>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
+        <v>stat(bullet_velocity;0.15;0.65;1500;3000)</v>
       </c>
       <c r="AD9" s="13">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="AE9" s="13">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="AF9" s="14">
         <v>1500</v>
@@ -2310,7 +2312,7 @@
       </c>
       <c r="AI9" s="11">
         <f t="shared" si="0"/>
-        <v>0.5829333333333333</v>
+        <v>0.38933333333333331</v>
       </c>
       <c r="AJ9" s="16">
         <v>34</v>
@@ -2336,11 +2338,11 @@
       </c>
       <c r="AP9" s="18">
         <f>(AI9-Model!$B$8)*Model!$B$38</f>
-        <v>-1.6682666666666668</v>
+        <v>-2.4426666666666668</v>
       </c>
       <c r="AQ9" s="18">
         <f t="shared" si="1"/>
-        <v>1.2317333333333438</v>
+        <v>0.45733333333334381</v>
       </c>
     </row>
     <row r="10" spans="1:43" ht="14.25" customHeight="1">
@@ -2433,14 +2435,14 @@
         <v>0.75</v>
       </c>
       <c r="AC10" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD10,";",'556-ammo'!$AE10,";",'556-ammo'!$AF10,";",'556-ammo'!$AG10,")")</f>
-        <v>stat(bullet_velocity;0;0.5;1500;3000)</v>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
+        <v>stat(bullet_velocity;0;0.4;1500;3000)</v>
       </c>
       <c r="AD10" s="13">
         <v>0</v>
       </c>
       <c r="AE10" s="13">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AF10" s="14">
         <v>1500</v>
@@ -2454,7 +2456,7 @@
       </c>
       <c r="AI10" s="11">
         <f t="shared" si="0"/>
-        <v>0.31433333333333335</v>
+        <v>0.25146666666666667</v>
       </c>
       <c r="AJ10" s="16">
         <v>30</v>
@@ -2480,11 +2482,11 @@
       </c>
       <c r="AP10" s="18">
         <f>(AI10-Model!$B$8)*Model!$B$38</f>
-        <v>-2.7426666666666666</v>
+        <v>-2.9941333333333331</v>
       </c>
       <c r="AQ10" s="18">
         <f t="shared" si="1"/>
-        <v>-5.7426666666666621</v>
+        <v>-5.9941333333333287</v>
       </c>
     </row>
     <row r="11" spans="1:43" ht="14.25" customHeight="1">
@@ -2577,14 +2579,14 @@
         <v>0.75</v>
       </c>
       <c r="AC11" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD11,";",'556-ammo'!$AE11,";",'556-ammo'!$AF11,";",'556-ammo'!$AG11,")")</f>
-        <v>stat(bullet_velocity;0.85;1.65;1500;3000)</v>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
+        <v>stat(bullet_velocity;1;1.5;1500;3000)</v>
       </c>
       <c r="AD11" s="13">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AE11" s="13">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" s="14">
         <v>1500</v>
@@ -2598,7 +2600,7 @@
       </c>
       <c r="AI11" s="11">
         <f t="shared" si="0"/>
-        <v>1.3262666666666667</v>
+        <v>1.2976666666666667</v>
       </c>
       <c r="AJ11" s="16">
         <v>29</v>
@@ -2624,11 +2626,11 @@
       </c>
       <c r="AP11" s="18">
         <f>(AI11-Model!$B$8)*Model!$B$38</f>
-        <v>1.3050666666666668</v>
+        <v>1.190666666666667</v>
       </c>
       <c r="AQ11" s="18">
         <f t="shared" si="1"/>
-        <v>-0.74493333333332457</v>
+        <v>-0.8593333333333244</v>
       </c>
     </row>
     <row r="12" spans="1:43" ht="14.25" customHeight="1">
@@ -2645,7 +2647,7 @@
         <v>0.04</v>
       </c>
       <c r="E12" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5">
         <v>1</v>
@@ -2721,14 +2723,14 @@
         <v>0.8</v>
       </c>
       <c r="AC12" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD12,";",'556-ammo'!$AE12,";",'556-ammo'!$AF12,";",'556-ammo'!$AG12,")")</f>
-        <v>stat(bullet_velocity;0.65;1.45;1500;3000)</v>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
+        <v>stat(bullet_velocity;0.75;1.25;1500;3000)</v>
       </c>
       <c r="AD12" s="13">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="AE12" s="13">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AF12" s="14">
         <v>1500</v>
@@ -2742,7 +2744,7 @@
       </c>
       <c r="AI12" s="11">
         <f t="shared" si="0"/>
-        <v>1.0729333333333333</v>
+        <v>1.0143333333333333</v>
       </c>
       <c r="AJ12" s="16">
         <v>31</v>
@@ -2752,7 +2754,7 @@
       </c>
       <c r="AL12" s="18">
         <f>C12*Model!$B$24+D12*Model!$B$25+E12*Model!$B$26+F12*Model!$B$27+G12*Model!$B$28+H12*Model!$B$29+I12*Model!$B$30+J12*Model!$B$31+K12*Model!$B$32</f>
-        <v>-1.65</v>
+        <v>-2.4500000000000002</v>
       </c>
       <c r="AM12" s="18">
         <f>(Z12-Model!$B$5)*Model!$B$35</f>
@@ -2768,11 +2770,11 @@
       </c>
       <c r="AP12" s="18">
         <f>(AI12-Model!$B$8)*Model!$B$38</f>
-        <v>0.29173333333333318</v>
+        <v>5.7333333333333236E-2</v>
       </c>
       <c r="AQ12" s="18">
         <f t="shared" si="1"/>
-        <v>1.4317333333333453</v>
+        <v>0.3973333333333452</v>
       </c>
     </row>
     <row r="13" spans="1:43" ht="14.25" customHeight="1">
@@ -2792,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="6">
         <v>-0.15</v>
@@ -2865,14 +2867,14 @@
         <v>0.8</v>
       </c>
       <c r="AC13" s="10" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'556-ammo'!$AD13,";",'556-ammo'!$AE13,";",'556-ammo'!$AF13,";",'556-ammo'!$AG13,")")</f>
-        <v>stat(bullet_velocity;0.6;1.4;1500;3000)</v>
+        <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
+        <v>stat(bullet_velocity;0.7;1.2;1500;3000)</v>
       </c>
       <c r="AD13" s="13">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AE13" s="13">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AF13" s="14">
         <v>1500</v>
@@ -2886,7 +2888,7 @@
       </c>
       <c r="AI13" s="11">
         <f t="shared" si="0"/>
-        <v>1.0229333333333333</v>
+        <v>0.96433333333333326</v>
       </c>
       <c r="AJ13" s="26">
         <v>39</v>
@@ -2896,7 +2898,7 @@
       </c>
       <c r="AL13" s="21">
         <f>C13*Model!$B$24+D13*Model!$B$25+E13*Model!$B$26+F13*Model!$B$27+G13*Model!$B$28+H13*Model!$B$29+I13*Model!$B$30+J13*Model!$B$31+K13*Model!$B$32</f>
-        <v>-1.9500000000000002</v>
+        <v>-2.5499999999999998</v>
       </c>
       <c r="AM13" s="21">
         <f>(Z13-Model!$B$5)*Model!$B$35</f>
@@ -2912,11 +2914,11 @@
       </c>
       <c r="AP13" s="21">
         <f>(AI13-Model!$B$8)*Model!$B$38</f>
-        <v>9.1733333333333E-2</v>
+        <v>-0.14266666666666694</v>
       </c>
       <c r="AQ13" s="21">
         <f t="shared" si="1"/>
-        <v>1.5917333333333414</v>
+        <v>0.75733333333334196</v>
       </c>
     </row>
     <row r="14" spans="1:43" ht="14.25" customHeight="1"/>
@@ -3951,8 +3953,8 @@
       <c r="A1" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="45"/>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1">
       <c r="A2" s="27"/>

--- a/changes/556-ammo-super.xlsx
+++ b/changes/556-ammo-super.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AC4AD4-B4CA-4543-941F-8C95A5A99EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94052AE9-BA44-47B8-B2CE-41C425D10A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="6">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AL4" s="21">
         <f>C4*Model!$B$24+D4*Model!$B$25+E4*Model!$B$26+F4*Model!$B$27+G4*Model!$B$28+H4*Model!$B$29+I4*Model!$B$30+J4*Model!$B$31+K4*Model!$B$32</f>
-        <v>-2.6</v>
+        <v>-2.4</v>
       </c>
       <c r="AM4" s="21">
         <f>(Z4-Model!$B$5)*Model!$B$35</f>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AQ4" s="21">
         <f t="shared" si="1"/>
-        <v>-2.6093333333333311</v>
+        <v>-2.4093333333333309</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="14.25" customHeight="1">
@@ -1636,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="6">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="E5" s="5">
         <v>-2</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AL5" s="18">
         <f>C5*Model!$B$24+D5*Model!$B$25+E5*Model!$B$26+F5*Model!$B$27+G5*Model!$B$28+H5*Model!$B$29+I5*Model!$B$30+J5*Model!$B$31+K5*Model!$B$32</f>
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="AM5" s="18">
         <f>(Z5-Model!$B$5)*Model!$B$35</f>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AQ5" s="18">
         <f t="shared" si="1"/>
-        <v>0.7222000000000004</v>
+        <v>0.32220000000000004</v>
       </c>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1">
@@ -1780,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="6">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E6" s="5">
         <v>-1</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AL6" s="21">
         <f>C6*Model!$B$24+D6*Model!$B$25+E6*Model!$B$26+F6*Model!$B$27+G6*Model!$B$28+H6*Model!$B$29+I6*Model!$B$30+J6*Model!$B$31+K6*Model!$B$32</f>
-        <v>2.4999999999999911E-2</v>
+        <v>0.42500000000000027</v>
       </c>
       <c r="AM6" s="21">
         <f>(Z6-Model!$B$5)*Model!$B$35</f>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AQ6" s="21">
         <f t="shared" si="1"/>
-        <v>-0.60099999999999365</v>
+        <v>-0.20099999999999341</v>
       </c>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1">
@@ -1924,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="6">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E7" s="5">
         <v>1</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="AL7" s="18">
         <f>C7*Model!$B$24+D7*Model!$B$25+E7*Model!$B$26+F7*Model!$B$27+G7*Model!$B$28+H7*Model!$B$29+I7*Model!$B$30+J7*Model!$B$31+K7*Model!$B$32</f>
-        <v>-2.4500000000000002</v>
+        <v>-2.25</v>
       </c>
       <c r="AM7" s="18">
         <f>(Z7-Model!$B$5)*Model!$B$35</f>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AQ7" s="18">
         <f t="shared" si="1"/>
-        <v>-0.89933333333332444</v>
+        <v>-0.69933333333332426</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1">
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="6">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E8" s="5">
         <v>2</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AL8" s="18">
         <f>C8*Model!$B$24+D8*Model!$B$25+E8*Model!$B$26+F8*Model!$B$27+G8*Model!$B$28+H8*Model!$B$29+I8*Model!$B$30+J8*Model!$B$31+K8*Model!$B$32</f>
-        <v>-3.4000000000000004</v>
+        <v>-2.8000000000000003</v>
       </c>
       <c r="AM8" s="18">
         <f>(Z8-Model!$B$5)*Model!$B$35</f>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="AQ8" s="18">
         <f t="shared" si="1"/>
-        <v>-0.37486666666665824</v>
+        <v>0.2251333333333414</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="14.25" customHeight="1">
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="6">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E9" s="5">
         <v>1</v>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AL9" s="18">
         <f>C9*Model!$B$24+D9*Model!$B$25+E9*Model!$B$26+F9*Model!$B$27+G9*Model!$B$28+H9*Model!$B$29+I9*Model!$B$30+J9*Model!$B$31+K9*Model!$B$32</f>
-        <v>-1.7250000000000001</v>
+        <v>-1.5249999999999999</v>
       </c>
       <c r="AM9" s="18">
         <f>(Z9-Model!$B$5)*Model!$B$35</f>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AQ9" s="18">
         <f t="shared" si="1"/>
-        <v>0.45733333333334381</v>
+        <v>0.65733333333334398</v>
       </c>
     </row>
     <row r="10" spans="1:43" ht="14.25" customHeight="1">
@@ -2500,7 +2500,7 @@
         <v>-1</v>
       </c>
       <c r="D11" s="6">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" s="5">
         <v>1</v>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AL11" s="18">
         <f>C11*Model!$B$24+D11*Model!$B$25+E11*Model!$B$26+F11*Model!$B$27+G11*Model!$B$28+H11*Model!$B$29+I11*Model!$B$30+J11*Model!$B$31+K11*Model!$B$32</f>
-        <v>-0.64999999999999991</v>
+        <v>-0.85000000000000009</v>
       </c>
       <c r="AM11" s="18">
         <f>(Z11-Model!$B$5)*Model!$B$35</f>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="AQ11" s="18">
         <f t="shared" si="1"/>
-        <v>-0.8593333333333244</v>
+        <v>-1.0593333333333246</v>
       </c>
     </row>
     <row r="12" spans="1:43" ht="14.25" customHeight="1">
@@ -2644,7 +2644,7 @@
         <v>-1</v>
       </c>
       <c r="D12" s="6">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E12" s="5">
         <v>1</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AL12" s="18">
         <f>C12*Model!$B$24+D12*Model!$B$25+E12*Model!$B$26+F12*Model!$B$27+G12*Model!$B$28+H12*Model!$B$29+I12*Model!$B$30+J12*Model!$B$31+K12*Model!$B$32</f>
-        <v>-2.4500000000000002</v>
+        <v>-2.2500000000000004</v>
       </c>
       <c r="AM12" s="18">
         <f>(Z12-Model!$B$5)*Model!$B$35</f>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AQ12" s="18">
         <f t="shared" si="1"/>
-        <v>0.3973333333333452</v>
+        <v>0.59733333333334493</v>
       </c>
     </row>
     <row r="13" spans="1:43" ht="14.25" customHeight="1">
@@ -2788,7 +2788,7 @@
         <v>-1</v>
       </c>
       <c r="D13" s="6">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E13" s="5">
         <v>1</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AL13" s="21">
         <f>C13*Model!$B$24+D13*Model!$B$25+E13*Model!$B$26+F13*Model!$B$27+G13*Model!$B$28+H13*Model!$B$29+I13*Model!$B$30+J13*Model!$B$31+K13*Model!$B$32</f>
-        <v>-2.5499999999999998</v>
+        <v>-2.3500000000000005</v>
       </c>
       <c r="AM13" s="21">
         <f>(Z13-Model!$B$5)*Model!$B$35</f>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AQ13" s="21">
         <f t="shared" si="1"/>
-        <v>0.75733333333334196</v>
+        <v>0.95733333333334114</v>
       </c>
     </row>
     <row r="14" spans="1:43" ht="14.25" customHeight="1"/>

--- a/changes/556-ammo-super.xlsx
+++ b/changes/556-ammo-super.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94052AE9-BA44-47B8-B2CE-41C425D10A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A25511B-8A45-4D08-9915-9D4FF03AB70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="556-ammo" sheetId="1" r:id="rId1"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AN3" s="18">
         <f>(Model!$B$6-AA3)*Model!$B$36</f>
-        <v>-0.20000000000000007</v>
+        <v>0.20000000000000007</v>
       </c>
       <c r="AO3" s="18">
         <f>(AB3-Model!$B$7)*Model!$B$37</f>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AQ3" s="18">
         <f t="shared" ref="AQ3:AQ13" si="1">SUM(AL3:AP3)</f>
-        <v>-3.0009999999999959</v>
+        <v>-2.6009999999999955</v>
       </c>
     </row>
     <row r="4" spans="1:43" ht="14.25" customHeight="1">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AN4" s="21">
         <f>(Model!$B$6-AA4)*Model!$B$36</f>
-        <v>-0.10000000000000009</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AO4" s="21">
         <f>(AB4-Model!$B$7)*Model!$B$37</f>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AQ4" s="21">
         <f t="shared" si="1"/>
-        <v>-2.4093333333333309</v>
+        <v>-2.2093333333333307</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="14.25" customHeight="1">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AN5" s="18">
         <f>(Model!$B$6-AA5)*Model!$B$36</f>
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="AO5" s="18">
         <f>(AB5-Model!$B$7)*Model!$B$37</f>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AQ5" s="18">
         <f t="shared" si="1"/>
-        <v>0.32220000000000004</v>
+        <v>1.3222</v>
       </c>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="AN6" s="21">
         <f>(Model!$B$6-AA6)*Model!$B$36</f>
-        <v>-0.10000000000000009</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AO6" s="21">
         <f>(AB6-Model!$B$7)*Model!$B$37</f>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AQ6" s="21">
         <f t="shared" si="1"/>
-        <v>-0.20099999999999341</v>
+        <v>-9.9999999999322853E-4</v>
       </c>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AN7" s="18">
         <f>(Model!$B$6-AA7)*Model!$B$36</f>
-        <v>-0.10000000000000009</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AO7" s="18">
         <f>(AB7-Model!$B$7)*Model!$B$37</f>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AQ7" s="18">
         <f t="shared" si="1"/>
-        <v>-0.69933333333332426</v>
+        <v>-0.49933333333332408</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AN8" s="18">
         <f>(Model!$B$6-AA8)*Model!$B$36</f>
-        <v>0.19999999999999996</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="AO8" s="18">
         <f>(AB8-Model!$B$7)*Model!$B$37</f>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="AQ8" s="18">
         <f t="shared" si="1"/>
-        <v>0.2251333333333414</v>
+        <v>-0.17486666666665807</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="14.25" customHeight="1">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AN9" s="18">
         <f>(Model!$B$6-AA9)*Model!$B$36</f>
-        <v>-0.10000000000000009</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AO9" s="18">
         <f>(AB9-Model!$B$7)*Model!$B$37</f>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AQ9" s="18">
         <f t="shared" si="1"/>
-        <v>0.65733333333334398</v>
+        <v>0.85733333333334416</v>
       </c>
     </row>
     <row r="10" spans="1:43" ht="14.25" customHeight="1">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AN10" s="18">
         <f>(Model!$B$6-AA10)*Model!$B$36</f>
-        <v>-0.30000000000000004</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AO10" s="18">
         <f>(AB10-Model!$B$7)*Model!$B$37</f>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AQ10" s="18">
         <f t="shared" si="1"/>
-        <v>-5.9941333333333287</v>
+        <v>-5.394133333333329</v>
       </c>
     </row>
     <row r="11" spans="1:43" ht="14.25" customHeight="1">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AN11" s="18">
         <f>(Model!$B$6-AA11)*Model!$B$36</f>
-        <v>-0.20000000000000007</v>
+        <v>0.20000000000000007</v>
       </c>
       <c r="AO11" s="18">
         <f>(AB11-Model!$B$7)*Model!$B$37</f>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="AQ11" s="18">
         <f t="shared" si="1"/>
-        <v>-1.0593333333333246</v>
+        <v>-0.65933333333332422</v>
       </c>
     </row>
     <row r="12" spans="1:43" ht="14.25" customHeight="1">
@@ -4293,7 +4293,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="41">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="C36" s="40" t="s">
         <v>102</v>

--- a/changes/556-ammo-super.xlsx
+++ b/changes/556-ammo-super.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yifan/Documents/deadline-dev/deadline-balancing/changes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A25511B-8A45-4D08-9915-9D4FF03AB70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142687E3-ABC4-A74D-AED0-9408F1D37E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="556-ammo" sheetId="1" r:id="rId1"/>
@@ -108,9 +108,17 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Carlito"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">adjusted to make mk262 as accurate as m855a1 currently is ingame
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Carlito"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
         </r>
       </text>
@@ -475,7 +483,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -525,6 +533,11 @@
       <sz val="10"/>
       <color rgb="FF1F2933"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="14">
@@ -808,14 +821,20 @@
     <xf numFmtId="164" fontId="7" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -828,12 +847,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1134,77 +1147,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ999"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
-    <col min="2" max="2" width="20.25" customWidth="1"/>
-    <col min="3" max="8" width="5.625" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.1640625" customWidth="1"/>
+    <col min="3" max="8" width="5.6640625" customWidth="1"/>
     <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="28" width="5.625" customWidth="1"/>
+    <col min="10" max="28" width="5.6640625" customWidth="1"/>
     <col min="29" max="29" width="31" customWidth="1"/>
-    <col min="30" max="36" width="5.625" customWidth="1"/>
-    <col min="37" max="37" width="9.625" customWidth="1"/>
-    <col min="38" max="43" width="5.625" customWidth="1"/>
+    <col min="30" max="36" width="5.6640625" customWidth="1"/>
+    <col min="37" max="37" width="9.6640625" customWidth="1"/>
+    <col min="38" max="43" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="24" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="49" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="46"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="50" t="s">
+      <c r="S1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="49" t="s">
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="45"/>
-      <c r="AH1" s="51" t="s">
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
+      <c r="AD1" s="45"/>
+      <c r="AE1" s="45"/>
+      <c r="AF1" s="45"/>
+      <c r="AG1" s="46"/>
+      <c r="AH1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="45"/>
-      <c r="AJ1" s="44" t="s">
+      <c r="AI1" s="46"/>
+      <c r="AJ1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="45"/>
-      <c r="AL1" s="46" t="s">
+      <c r="AK1" s="46"/>
+      <c r="AL1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="47"/>
-      <c r="AO1" s="47"/>
-      <c r="AP1" s="47"/>
-      <c r="AQ1" s="45"/>
+      <c r="AM1" s="45"/>
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="45"/>
+      <c r="AP1" s="45"/>
+      <c r="AQ1" s="46"/>
     </row>
     <row r="2" spans="1:43" ht="45.75" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -1428,13 +1441,13 @@
       </c>
       <c r="AC3" s="10" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.3;0.8;1500;3000)</v>
+        <v>stat(bullet_velocity;0.25;0.75;1500;3000)</v>
       </c>
       <c r="AD3" s="13">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="AE3" s="13">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AF3" s="14">
         <v>1500</v>
@@ -1444,11 +1457,11 @@
       </c>
       <c r="AH3" s="15">
         <f>Model!$B$4+IF(I3="",0,I3)</f>
-        <v>2343</v>
+        <v>2483</v>
       </c>
       <c r="AI3" s="11">
         <f t="shared" ref="AI3:AI13" si="0">MAX(AD3,MIN(AE3,AD3+(AH3-AF3)*(AE3-AD3)/(AG3-AF3)))</f>
-        <v>0.58099999999999996</v>
+        <v>0.57766666666666666</v>
       </c>
       <c r="AJ3" s="16">
         <v>36</v>
@@ -1474,11 +1487,11 @@
       </c>
       <c r="AP3" s="18">
         <f>(AI3-Model!$B$8)*Model!$B$38</f>
-        <v>-1.6760000000000002</v>
+        <v>-1.6893333333333334</v>
       </c>
       <c r="AQ3" s="18">
         <f t="shared" ref="AQ3:AQ13" si="1">SUM(AL3:AP3)</f>
-        <v>-2.6009999999999955</v>
+        <v>-2.6143333333333292</v>
       </c>
     </row>
     <row r="4" spans="1:43" ht="14.25" customHeight="1">
@@ -1588,11 +1601,11 @@
       </c>
       <c r="AH4" s="15">
         <f>Model!$B$4+IF(I4="",0,I4)</f>
-        <v>2243</v>
+        <v>2383</v>
       </c>
       <c r="AI4" s="11">
         <f t="shared" si="0"/>
-        <v>0.64766666666666672</v>
+        <v>0.69433333333333336</v>
       </c>
       <c r="AJ4" s="19">
         <v>38</v>
@@ -1618,11 +1631,11 @@
       </c>
       <c r="AP4" s="21">
         <f>(AI4-Model!$B$8)*Model!$B$38</f>
-        <v>-1.4093333333333331</v>
+        <v>-1.2226666666666666</v>
       </c>
       <c r="AQ4" s="21">
         <f t="shared" si="1"/>
-        <v>-2.2093333333333307</v>
+        <v>-2.0226666666666642</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="14.25" customHeight="1">
@@ -1732,11 +1745,11 @@
       </c>
       <c r="AH5" s="15">
         <f>Model!$B$4+IF(I5="",0,I5)</f>
-        <v>2743</v>
+        <v>2883</v>
       </c>
       <c r="AI5" s="11">
         <f t="shared" si="0"/>
-        <v>0.12429999999999999</v>
+        <v>0.13830000000000001</v>
       </c>
       <c r="AJ5" s="16">
         <v>35</v>
@@ -1762,11 +1775,11 @@
       </c>
       <c r="AP5" s="18">
         <f>(AI5-Model!$B$8)*Model!$B$38</f>
-        <v>-3.5028000000000001</v>
+        <v>-3.4468000000000001</v>
       </c>
       <c r="AQ5" s="18">
         <f t="shared" si="1"/>
-        <v>1.3222</v>
+        <v>1.3782000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1">
@@ -1860,13 +1873,13 @@
       </c>
       <c r="AC6" s="10" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.35;0.85;1500;3000)</v>
+        <v>stat(bullet_velocity;0.3;0.8;1500;3000)</v>
       </c>
       <c r="AD6" s="13">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="AE6" s="13">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="AF6" s="14">
         <v>1500</v>
@@ -1876,11 +1889,11 @@
       </c>
       <c r="AH6" s="25">
         <f>Model!$B$4+IF(I6="",0,I6)</f>
-        <v>2268</v>
+        <v>2408</v>
       </c>
       <c r="AI6" s="24">
         <f t="shared" si="0"/>
-        <v>0.60599999999999998</v>
+        <v>0.60266666666666668</v>
       </c>
       <c r="AJ6" s="19">
         <v>37</v>
@@ -1906,11 +1919,11 @@
       </c>
       <c r="AP6" s="21">
         <f>(AI6-Model!$B$8)*Model!$B$38</f>
-        <v>-1.5760000000000001</v>
+        <v>-1.5893333333333333</v>
       </c>
       <c r="AQ6" s="21">
         <f t="shared" si="1"/>
-        <v>-9.9999999999322853E-4</v>
+        <v>-1.4333333333326426E-2</v>
       </c>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1">
@@ -1933,11 +1946,11 @@
         <v>1</v>
       </c>
       <c r="G7" s="6">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="5">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="8">
@@ -1997,20 +2010,20 @@
         <v>52.040000000000006</v>
       </c>
       <c r="AA7" s="12">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="AB7" s="12">
         <v>0.85</v>
       </c>
       <c r="AC7" s="10" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.35;0.85;1500;3000)</v>
+        <v>stat(bullet_velocity;0.4;0.9;1500;3000)</v>
       </c>
       <c r="AD7" s="13">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="AE7" s="13">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="AF7" s="14">
         <v>1500</v>
@@ -2020,11 +2033,11 @@
       </c>
       <c r="AH7" s="15">
         <f>Model!$B$4+IF(I7="",0,I7)</f>
-        <v>2393</v>
+        <v>2583</v>
       </c>
       <c r="AI7" s="11">
         <f t="shared" si="0"/>
-        <v>0.64766666666666661</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="AJ7" s="16">
         <v>32</v>
@@ -2034,7 +2047,7 @@
       </c>
       <c r="AL7" s="18">
         <f>C7*Model!$B$24+D7*Model!$B$25+E7*Model!$B$26+F7*Model!$B$27+G7*Model!$B$28+H7*Model!$B$29+I7*Model!$B$30+J7*Model!$B$31+K7*Model!$B$32</f>
-        <v>-2.25</v>
+        <v>-1.5</v>
       </c>
       <c r="AM7" s="18">
         <f>(Z7-Model!$B$5)*Model!$B$35</f>
@@ -2042,7 +2055,7 @@
       </c>
       <c r="AN7" s="18">
         <f>(Model!$B$6-AA7)*Model!$B$36</f>
-        <v>0.10000000000000009</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="18">
         <f>(AB7-Model!$B$7)*Model!$B$37</f>
@@ -2050,11 +2063,11 @@
       </c>
       <c r="AP7" s="18">
         <f>(AI7-Model!$B$8)*Model!$B$38</f>
-        <v>-1.4093333333333335</v>
+        <v>-0.95599999999999996</v>
       </c>
       <c r="AQ7" s="18">
         <f t="shared" si="1"/>
-        <v>-0.49933333333332408</v>
+        <v>0.60400000000000942</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1">
@@ -2065,7 +2078,7 @@
         <v>60</v>
       </c>
       <c r="C8" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D8" s="6">
         <v>0.08</v>
@@ -2074,7 +2087,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="6">
         <v>-0.2</v>
@@ -2148,13 +2161,13 @@
       </c>
       <c r="AC8" s="10" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0;0.35;1500;3000)</v>
+        <v>stat(bullet_velocity;0;0.3;1500;3000)</v>
       </c>
       <c r="AD8" s="13">
         <v>0</v>
       </c>
       <c r="AE8" s="13">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="AF8" s="14">
         <v>1500</v>
@@ -2164,11 +2177,11 @@
       </c>
       <c r="AH8" s="15">
         <f>Model!$B$4+IF(I8="",0,I8)</f>
-        <v>2143</v>
+        <v>2283</v>
       </c>
       <c r="AI8" s="11">
         <f t="shared" si="0"/>
-        <v>0.15003333333333332</v>
+        <v>0.15659999999999999</v>
       </c>
       <c r="AJ8" s="16">
         <v>28</v>
@@ -2178,7 +2191,7 @@
       </c>
       <c r="AL8" s="18">
         <f>C8*Model!$B$24+D8*Model!$B$25+E8*Model!$B$26+F8*Model!$B$27+G8*Model!$B$28+H8*Model!$B$29+I8*Model!$B$30+J8*Model!$B$31+K8*Model!$B$32</f>
-        <v>-2.8000000000000003</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="AM8" s="18">
         <f>(Z8-Model!$B$5)*Model!$B$35</f>
@@ -2194,11 +2207,11 @@
       </c>
       <c r="AP8" s="18">
         <f>(AI8-Model!$B$8)*Model!$B$38</f>
-        <v>-3.3998666666666666</v>
+        <v>-3.3736000000000002</v>
       </c>
       <c r="AQ8" s="18">
         <f t="shared" si="1"/>
-        <v>-0.17486666666665807</v>
+        <v>-1.7485999999999919</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="14.25" customHeight="1">
@@ -2308,11 +2321,11 @@
       </c>
       <c r="AH9" s="15">
         <f>Model!$B$4+IF(I9="",0,I9)</f>
-        <v>2218</v>
+        <v>2358</v>
       </c>
       <c r="AI9" s="11">
         <f t="shared" si="0"/>
-        <v>0.38933333333333331</v>
+        <v>0.43599999999999994</v>
       </c>
       <c r="AJ9" s="16">
         <v>34</v>
@@ -2338,11 +2351,11 @@
       </c>
       <c r="AP9" s="18">
         <f>(AI9-Model!$B$8)*Model!$B$38</f>
-        <v>-2.4426666666666668</v>
+        <v>-2.2560000000000002</v>
       </c>
       <c r="AQ9" s="18">
         <f t="shared" si="1"/>
-        <v>0.85733333333334416</v>
+        <v>1.0440000000000107</v>
       </c>
     </row>
     <row r="10" spans="1:43" ht="14.25" customHeight="1">
@@ -2436,13 +2449,13 @@
       </c>
       <c r="AC10" s="10" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0;0.4;1500;3000)</v>
+        <v>stat(bullet_velocity;0;0.35;1500;3000)</v>
       </c>
       <c r="AD10" s="13">
         <v>0</v>
       </c>
       <c r="AE10" s="13">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="AF10" s="14">
         <v>1500</v>
@@ -2452,11 +2465,11 @@
       </c>
       <c r="AH10" s="15">
         <f>Model!$B$4+IF(I10="",0,I10)</f>
-        <v>2443</v>
+        <v>2583</v>
       </c>
       <c r="AI10" s="11">
         <f t="shared" si="0"/>
-        <v>0.25146666666666667</v>
+        <v>0.25269999999999998</v>
       </c>
       <c r="AJ10" s="16">
         <v>30</v>
@@ -2482,11 +2495,11 @@
       </c>
       <c r="AP10" s="18">
         <f>(AI10-Model!$B$8)*Model!$B$38</f>
-        <v>-2.9941333333333331</v>
+        <v>-2.9892000000000003</v>
       </c>
       <c r="AQ10" s="18">
         <f t="shared" si="1"/>
-        <v>-5.394133333333329</v>
+        <v>-5.3891999999999962</v>
       </c>
     </row>
     <row r="11" spans="1:43" ht="14.25" customHeight="1">
@@ -2580,13 +2593,13 @@
       </c>
       <c r="AC11" s="10" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;1;1.5;1500;3000)</v>
+        <v>stat(bullet_velocity;0.9;1.4;1500;3000)</v>
       </c>
       <c r="AD11" s="13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AE11" s="13">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF11" s="14">
         <v>1500</v>
@@ -2596,11 +2609,11 @@
       </c>
       <c r="AH11" s="15">
         <f>Model!$B$4+IF(I11="",0,I11)</f>
-        <v>2393</v>
+        <v>2533</v>
       </c>
       <c r="AI11" s="11">
         <f t="shared" si="0"/>
-        <v>1.2976666666666667</v>
+        <v>1.2443333333333333</v>
       </c>
       <c r="AJ11" s="16">
         <v>29</v>
@@ -2626,11 +2639,11 @@
       </c>
       <c r="AP11" s="18">
         <f>(AI11-Model!$B$8)*Model!$B$38</f>
-        <v>1.190666666666667</v>
+        <v>0.97733333333333317</v>
       </c>
       <c r="AQ11" s="18">
         <f t="shared" si="1"/>
-        <v>-0.65933333333332422</v>
+        <v>-0.87266666666665804</v>
       </c>
     </row>
     <row r="12" spans="1:43" ht="14.25" customHeight="1">
@@ -2724,13 +2737,13 @@
       </c>
       <c r="AC12" s="10" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.75;1.25;1500;3000)</v>
+        <v>stat(bullet_velocity;0.7;1.2;1500;3000)</v>
       </c>
       <c r="AD12" s="13">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="AE12" s="13">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF12" s="14">
         <v>1500</v>
@@ -2740,11 +2753,11 @@
       </c>
       <c r="AH12" s="15">
         <f>Model!$B$4+IF(I12="",0,I12)</f>
-        <v>2293</v>
+        <v>2433</v>
       </c>
       <c r="AI12" s="11">
         <f t="shared" si="0"/>
-        <v>1.0143333333333333</v>
+        <v>1.0109999999999999</v>
       </c>
       <c r="AJ12" s="16">
         <v>31</v>
@@ -2770,11 +2783,11 @@
       </c>
       <c r="AP12" s="18">
         <f>(AI12-Model!$B$8)*Model!$B$38</f>
-        <v>5.7333333333333236E-2</v>
+        <v>4.3999999999999595E-2</v>
       </c>
       <c r="AQ12" s="18">
         <f t="shared" si="1"/>
-        <v>0.59733333333334493</v>
+        <v>0.58400000000001129</v>
       </c>
     </row>
     <row r="13" spans="1:43" ht="14.25" customHeight="1">
@@ -2791,10 +2804,10 @@
         <v>0.03</v>
       </c>
       <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5">
         <v>1</v>
-      </c>
-      <c r="F13" s="5">
-        <v>2</v>
       </c>
       <c r="G13" s="6">
         <v>-0.15</v>
@@ -2868,13 +2881,13 @@
       </c>
       <c r="AC13" s="10" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",Table_1[[#This Row],[pen_low]],";",Table_1[[#This Row],[pen_high]],";",Table_1[[#This Row],[pen_velocity_low]],";",Table_1[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.7;1.2;1500;3000)</v>
+        <v>stat(bullet_velocity;0.65;1.15;1500;3000)</v>
       </c>
       <c r="AD13" s="13">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="AE13" s="13">
-        <v>1.2</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AF13" s="14">
         <v>1500</v>
@@ -2884,11 +2897,11 @@
       </c>
       <c r="AH13" s="15">
         <f>Model!$B$4+IF(I13="",0,I13)</f>
-        <v>2293</v>
+        <v>2433</v>
       </c>
       <c r="AI13" s="11">
         <f t="shared" si="0"/>
-        <v>0.96433333333333326</v>
+        <v>0.96099999999999997</v>
       </c>
       <c r="AJ13" s="26">
         <v>39</v>
@@ -2898,7 +2911,7 @@
       </c>
       <c r="AL13" s="21">
         <f>C13*Model!$B$24+D13*Model!$B$25+E13*Model!$B$26+F13*Model!$B$27+G13*Model!$B$28+H13*Model!$B$29+I13*Model!$B$30+J13*Model!$B$31+K13*Model!$B$32</f>
-        <v>-2.3500000000000005</v>
+        <v>-2.5500000000000003</v>
       </c>
       <c r="AM13" s="21">
         <f>(Z13-Model!$B$5)*Model!$B$35</f>
@@ -2914,11 +2927,11 @@
       </c>
       <c r="AP13" s="21">
         <f>(AI13-Model!$B$8)*Model!$B$38</f>
-        <v>-0.14266666666666694</v>
+        <v>-0.15600000000000014</v>
       </c>
       <c r="AQ13" s="21">
         <f t="shared" si="1"/>
-        <v>0.95733333333334114</v>
+        <v>0.74400000000000832</v>
       </c>
     </row>
     <row r="14" spans="1:43" ht="14.25" customHeight="1"/>
@@ -3941,20 +3954,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C1000"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="26" width="8.625" customWidth="1"/>
+    <col min="4" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.5" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="45"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="46"/>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1">
       <c r="A2" s="27"/>
@@ -3977,7 +3990,7 @@
         <v>75</v>
       </c>
       <c r="B4" s="30">
-        <v>2343</v>
+        <v>2483</v>
       </c>
       <c r="C4" s="31" t="s">
         <v>76</v>
@@ -4033,11 +4046,11 @@
       <c r="C9" s="31"/>
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="55"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="49"/>
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1">
       <c r="A11" s="31"/>
@@ -4148,11 +4161,11 @@
       <c r="C21" s="31"/>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="55"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" s="33" t="s">
@@ -4271,11 +4284,11 @@
       <c r="C33" s="31"/>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="B34" s="54"/>
-      <c r="C34" s="55"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="49"/>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1">
       <c r="A35" s="40" t="s">
